--- a/results/joey/LATAM/Week_of_2026-07-20/Scored_LATAM_Joey_Complete_2026-07-20.xlsx
+++ b/results/joey/LATAM/Week_of_2026-07-20/Scored_LATAM_Joey_Complete_2026-07-20.xlsx
@@ -820,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="AB2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -834,11 +834,15 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Director-level payer GTM operations role in US value-based care, a healthcare-specific domain outside Joey's fintech/VC/government background, and the posting is listed simply as "Remote, United States" with no LATAM or international-candidate language.</t>
+          <t>Director-level GTM/operations role has real structural overlap with Joey's cross-functional program work, but it is healthcare-payer domain-gated (value-based care, ACOs, Medicare Advantage) with no LATAM signal. Location is explicitly "Remote, United States," a hard geographic disqualifier.</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Domain, Geography</t>
+        </is>
+      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>not_mentioned</t>
@@ -870,16 +874,16 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1013,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="AB3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -1027,11 +1031,15 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>This is an individual-contributor GTM systems-builder/CSM role at the 4+ year level, not a Director/VP-caliber strategy or partnerships position, and it is posted as "Remote, United States" with pay tiers scoped to US locations only.</t>
+          <t>This is an individual-contributor "GTM Engineer" role (4+ years, book-of-accounts CSM/RevOps hybrid), well below Joey's Director/SVP calibration and outside his sector focus. Location is "Remote, United States" with no LATAM mention, a hard disqualifier.</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Function, Level, Geography</t>
+        </is>
+      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>not_mentioned</t>
@@ -1044,7 +1052,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>130000-165000</t>
+          <t>$130,000-$165,000</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1069,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>6</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1206,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="AB4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -1220,11 +1228,15 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Despite executive-facing multithreading responsibilities, this is a 6+ year individual-contributor account role rather than a Director+ position, and the listing is "Remote, United States" with pay tiers explicitly scoped to US locations.</t>
+          <t>Mid-Market GTM Engineer is a senior IC account-management role (6+ years) requiring "3+ stakeholders per account" multithreading, not a Director-level strategy or CoS mandate. Location is "Remote, United States," a hard geographic disqualifier with no LATAM scope stated.</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Function, Level, Geography</t>
+        </is>
+      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>not_mentioned</t>
@@ -1237,7 +1249,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>150000-175000</t>
+          <t>$150,000-$175,000</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1256,16 +1268,16 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -1399,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="AB5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1413,11 +1425,15 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>The Head of Growth Marketing scope and executive exposure are a reasonable operator fit, but the JD states candidates "must be legally authorized to work in the United States" even under the "Remote (Americas)" option, which contradicts genuine LATAM openness.</t>
+          <t>"Remote (Americas, UTC-3 to UTC-10)" reads LATAM-open, but the JD states candidates "must be legally authorized to work in the United States" with no sponsorship, which is a US-residency disqualifier regardless of the timezone framing. The role itself is also a hands-on growth-marketing/channel-ops seat (SEO, content, paid channels), a domain and function stretch from Joey's CoS/BizOps/partnerships background.</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Domain, Function, Geography</t>
+        </is>
+      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>not_mentioned</t>
@@ -1430,7 +1446,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>200000-250000</t>
+          <t>$200,000-$250,000</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1440,7 +1456,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Eric (growth strategy owner) - no formal title given</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1449,13 +1465,13 @@
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
@@ -1592,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="AB6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1606,11 +1622,15 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Strong program-management/cross-functional skills match, but the listing is titled "Remote, Bangalore" and requires applicants to confirm they are currently based in Bangalore, with no LATAM or open-remote signal.</t>
+          <t>The cross-functional program-management scope (IT/Finance/Legal stakeholders, governance frameworks) echoes Joey's DoD program-management background reasonably well, but the posting is anchored to a specific non-LATAM city, asking "Are you currently based in Bangalore?" This is a hard geographic disqualifier with zero LATAM relevance in the enterprise DevSecOps/IT domain.</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Domain, Geography</t>
+        </is>
+      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>not_mentioned</t>
@@ -1642,7 +1662,7 @@
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1651,7 +1671,7 @@
         <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -1799,15 +1819,11 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Location is stated as "Remote, US" with no LATAM signal, and the role is a Finance-native transformation mandate (SOX, Lead-to-Cash, billing architecture) outside Joey's BD/CoS background. Disqualified on geography.</t>
+          <t>Explicitly listed as "Remote, US" with no international-candidate language, so this is a US work-location role outside LATAM scope. It is also a Finance-domain-owned VP role (SOX, revenue recognition, Lead-to-Cash) rather than a general CoS/ops/partnerships mandate.</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>Domain, Geography</t>
-        </is>
-      </c>
+      <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr">
         <is>
           <t>not_mentioned</t>
@@ -1825,7 +1841,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>us_level</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -1835,7 +1851,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>zero_to_one</t>
+          <t>scale_existing</t>
         </is>
       </c>
       <c r="AN7" t="n">
@@ -1845,10 +1861,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1996,15 +2012,11 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Explicitly "Remote, United States" with E-Verify/I-9 language confirming US-only hiring, and the role is a hands-on technical GTM engineering IC job (Clay/Claude workflow-building) unrelated to Joey's strategic operator background. Disqualified on geography.</t>
+          <t>Location is stated as "Remote, United States" with an E-Verify/I-9 requirement, placing it outside LATAM scope. The role itself is a hands-on technical GTM engineering IC position (Clay, APIs, prompt workflows), not a CoS/Country Manager/senior BD match.</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>Function, Domain, Geography</t>
-        </is>
-      </c>
+      <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr">
         <is>
           <t>not_mentioned</t>
@@ -2017,7 +2029,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>130000-180000</t>
+          <t>$130,000 - $180,000 USD per year</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2042,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ8" t="n">
         <v>5</v>
@@ -2193,15 +2205,11 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Listed as "Remote" but salary bands are scoped entirely to US labor-cost zones (Zone A-C cities) with Zone D explicitly unfunded, indicating a US-only hire; the role is also a Manager-level enablement/training function reporting to a Director, below Joey's target seniority. Disqualified on geography.</t>
+          <t>Salary band is scoped to US geographic zones ("Zones A-C"), indicating a US work location despite the bare "Remote" location string. Seniority sits below Director as an individual GTM Enablement Manager, and the function (training/enablement content) is a partial match at best to Joey's CoS/partnerships/ops background.</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>Function, Level, Geography</t>
-        </is>
-      </c>
+      <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr">
         <is>
           <t>not_mentioned</t>
@@ -2214,7 +2222,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>108650-142224</t>
+          <t>$108,650.00 - $142,224.00</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2233,7 +2241,7 @@
         </is>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2390,15 +2398,11 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Role is bound to "Remote, UK" and requires personally building the EMEA region hands-on with no LATAM scope stated; sector is ad-tech/performance marketing, listed as a poor fit under the rubric. Disqualified on geography.</t>
+          <t>Role is explicitly scoped to "Remote, UK" / EMEA with country-of-residence and work-authorization screening questions, entirely outside LATAM geography. It also requires a specific must-have background "building out EMEA for an ad-tech company," a domain Joey hasn't worked in.</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
+      <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr">
         <is>
           <t>not_mentioned</t>
@@ -2430,13 +2434,13 @@
         </is>
       </c>
       <c r="AN10" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ10" t="n">
         <v>5</v>
@@ -2587,15 +2591,11 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Location is "Remote - NY" and the JD requires work authorization in the US without sponsorship, with no LATAM signal; the individual-contributor Manager scope (4-6 years experience framing) also sits below Joey's target seniority. Disqualified on geography.</t>
+          <t>JD states candidates "must be authorized to work in the United States without... sponsorship," confirming a US-only work location. The role is also explicitly an individual-contributor position requiring hospital-RCM/IDR domain SME and SQL/BigQuery fluency, a significant domain and technical gap from Joey's background.</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>Level, Geography</t>
-        </is>
-      </c>
+      <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr">
         <is>
           <t>not_mentioned</t>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>120000-150000</t>
+          <t>$120K - $150K</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="AN11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
         <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2784,13 +2784,13 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Role is restricted to 'Remote - DACH' with deep German payroll/DATEV requirements, giving no LATAM signal despite Remote.com's EOR/cross-border sector fit. It is also a payroll-implementation specialist track reporting to a Payroll Operations manager, not a CoS/BD/strategy function.</t>
+          <t>Role is restricted to 'Remote - DACH,' a specific non-LATAM regional lock with no stated LATAM openness. It is also a payroll-implementation specialist function (DATEV expertise, German legislative knowledge) rather than the CoS/BD/strategic-ops work Joey targets.</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Function, Level</t>
+          <t>function, domain</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>$77,600-$87,300 (converted from EUR71,850-EUR80,800)</t>
+          <t>approx $77,600-$87,300 (from €71,850-€80,800 EUR)</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2981,13 +2981,13 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Rula states it hires in 'most U.S. states' with no LATAM or international remote option, and the role is a SQL-heavy provider-quality Manager position rather than an executive-facing strategy/BD mandate. Sector (mental healthcare) also carries no stated LATAM relevance.</t>
+          <t>JD explicitly states the company hires only within the U.S. ('must be based in United States, currently not hiring in Hawaii'), which is a hard geo_restricted disqualifier regardless of fit. Underlying function (strategy &amp; ops, data-driven programs) is a partial skills match but the mental-healthcare sector isn't among Joey's priority verticals.</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>Function, Domain, Level</t>
+          <t>geography</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -3027,10 +3027,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -3178,13 +3178,13 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Upwork states it hires full-time employees in only '34 U.S. states' with a Palo Alto home base, giving no LATAM or open-remote signal despite a strong Sr Director-level strategy/BD fit. The role's core function is hands-on M&amp;A sourcing and integration execution, a step beyond Joey's partnerships/financing-deal background.</t>
+          <t>JD asks for current/planned U.S. state of residence and the company hires full-time only across 34 U.S. states, a geo_restricted disqualifier with no LATAM or international remote path stated. Sr. Director-level scope and executive exposure fit Joey's seniority, but hands-on M&amp;A/corp-dev deal execution is a domain stretch beyond his banking and partnerships background.</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Function, Geography</t>
+          <t>domain, geography</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="AN14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>19</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/results/joey/LATAM/Week_of_2026-07-20/Scored_LATAM_Joey_Complete_2026-07-20.xlsx
+++ b/results/joey/LATAM/Week_of_2026-07-20/Scored_LATAM_Joey_Complete_2026-07-20.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2A44"/>
         <bgColor rgb="001F2A44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
+        <bgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,10 +431,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ14"/>
+  <dimension ref="A1:AQ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
@@ -451,17 +458,17 @@
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="17" customWidth="1" min="23" max="23"/>
     <col width="31" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="31" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
     <col width="12" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="21" customWidth="1" min="33" max="33"/>
     <col width="21" customWidth="1" min="34" max="34"/>
-    <col width="16" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
     <col width="45" customWidth="1" min="36" max="36"/>
     <col width="16" customWidth="1" min="37" max="37"/>
     <col width="45" customWidth="1" min="38" max="38"/>
@@ -692,52 +699,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>portfolio_board:qed-investors</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>aledade</t>
+          <t>caliza</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aledade</t>
+          <t>caliza</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Director, Payer Go-To-Market (GTM), Remote</t>
+          <t>Mexico - Director of Business Development</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>growth_commercial</t>
+          <t>partnerships_bd</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Remote, United States</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>L?, D?, P?</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -745,11 +752,7 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -767,34 +770,26 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>needs_verification</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/aledade/660b03e4-e1db-4ac2-bb9e-c74666f52189</t>
+          <t>https://jobs.lever.co/caliza-financial-technologies/d3c4c930-0549-4dff-8b09-1fa9bee518a4</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-07-07T12:00:31.868000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Lever</t>
-        </is>
-      </c>
+          <t>2026-05-08T05:45:51.939000Z</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>api-live</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
@@ -803,12 +798,12 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>jd_cache/c70c44df4ecea1de.txt</t>
+          <t>jd_cache/e68b8ab33da2203c.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>portfolio_board:qed-investors</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -817,40 +812,32 @@
         </is>
       </c>
       <c r="AA2" t="n">
+        <v>83</v>
+      </c>
+      <c r="AB2" t="b">
         <v>0</v>
       </c>
-      <c r="AB2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>geo_restricted</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>skip</t>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Director-level GTM/operations role has real structural overlap with Joey's cross-functional program work, but it is healthcare-payer domain-gated (value-based care, ACOs, Medicare Advantage) with no LATAM signal. Location is explicitly "Remote, United States," a hard geographic disqualifier.</t>
+          <t>Director of Business Development for a stablecoin/cross-border fintech based in Mexico City is a direct sector, seniority, and geography match to Joey's background in startup banking and partnerships. Spanish fluency is explicitly required, which flags but doesn't disqualify given his active learning.</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Domain, Geography</t>
-        </is>
-      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>not_mentioned</t>
+          <t>required</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>geo_restricted</t>
+          <t>CDMX-Based</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -865,56 +852,56 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>not_stated</t>
+          <t>Head of Sales</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>scale_existing</t>
+          <t>zero_to_one</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP2" t="n">
         <v>18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>portfolio_board:a16z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>apolloio</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Apolloio</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Go-To-Market Engineer I, SMB</t>
+          <t>Strategic Programs Lead, New Markets</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>growth_commercial</t>
+          <t>strategic_ops</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Remote, United States</t>
+          <t>US-Remote</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -969,29 +956,21 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/apolloio/jobs/5778017004</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8070648</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-07-06T18:51:37-04:00</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
+          <t>2026-07-16T21:33:48Z</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>api-live</t>
-        </is>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
@@ -1000,12 +979,12 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>jd_cache/44f748fbd9b679ad.txt</t>
+          <t>jd_cache/27c007c7f953372d.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>portfolio_board:a16z</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1014,16 +993,12 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AB3" t="b">
         <v>1</v>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>geo_restricted</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
           <t>skip</t>
@@ -1031,13 +1006,13 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>This is an individual-contributor "GTM Engineer" role (4+ years, book-of-accounts CSM/RevOps hybrid), well below Joey's Director/SVP calibration and outside his sector focus. Location is "Remote, United States" with no LATAM mention, a hard disqualifier.</t>
+          <t>Strong functional match as a 0-to-1 strategic program lead at a fintech (Stripe) with explicit new-markets/Americas &amp; EMEA scope, but the role is US-remote with no LATAM residency path and requires deep risk/compliance program management domain not on Joey's resume. Two stretches (geography, domain) cap the score.</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Function, Level, Geography</t>
+          <t>Geography, Domain</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -1047,12 +1022,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>geo_restricted</t>
+          <t>Remote-Global-Open</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>$130,000-$165,000</t>
+          <t>$127,600 - $191,400 USD</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1067,20 +1042,20 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>scale_existing</t>
+          <t>zero_to_one</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -1091,27 +1066,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>apolloio</t>
+          <t>pivotal-health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Apolloio</t>
+          <t>Pivotal Health</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Go-To-Market Engineer II, Mid-Market</t>
+          <t>Client Strategy &amp; Operations Manager</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>growth_commercial</t>
+          <t>strategic_ops</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Remote, United States</t>
+          <t>Remote - NY</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1156,7 +1131,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1166,17 +1141,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/apolloio/jobs/5918855004</t>
+          <t>https://jobs.ashbyhq.com/pivotal-health/ce4e43d1-7add-408b-ae2d-c1205509527d</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-07-06T18:51:37-04:00</t>
+          <t>2026-05-20T22:25:49.748+00:00</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Ashby</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1197,7 +1172,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>jd_cache/52d4d3fd7ddd92f2.txt</t>
+          <t>jd_cache/00f0fa111ce5ea70.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1211,16 +1186,12 @@
         </is>
       </c>
       <c r="AA4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB4" t="b">
         <v>0</v>
       </c>
-      <c r="AB4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>geo_restricted</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
           <t>skip</t>
@@ -1228,13 +1199,13 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Mid-Market GTM Engineer is a senior IC account-management role (6+ years) requiring "3+ stakeholders per account" multithreading, not a Director-level strategy or CoS mandate. Location is "Remote, United States," a hard geographic disqualifier with no LATAM scope stated.</t>
+          <t>Individual-contributor client strategy/ops role requiring deep hospital revenue-cycle SME experience and strong SQL/BigQuery fluency Joey doesn't demonstrate, with US-only work authorization required and no LATAM signal.</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Function, Level, Geography</t>
+          <t>Function, Domain</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1244,12 +1215,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>geo_restricted</t>
+          <t>Remote-Global-Open</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>$150,000-$175,000</t>
+          <t>$120,000 - $150,000 USD</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1262,22 +1233,18 @@
           <t>not_stated</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>scale_existing</t>
-        </is>
-      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1288,17 +1255,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>firecrawl</t>
+          <t>includedhealth</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Firecrawl</t>
+          <t>Includedhealth</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Head of Growth Marketing</t>
+          <t>Go-To-Market Enablement Manager</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1308,7 +1275,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>San Francisco, CA (Hybrid) OR Remote (Americas, UTC-3 to UTC-10)</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1353,7 +1320,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1363,17 +1330,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/firecrawl/252206c1-56a2-4598-abef-d2ed9e2295de</t>
+          <t>https://jobs.lever.co/includedhealth/e5475693-8b26-4166-ad01-db9bcbbf2f96</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-07-13T00:04:16.535+00:00</t>
+          <t>2026-06-26T15:26:50.581000</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Ashby</t>
+          <t>Lever</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1394,7 +1361,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>jd_cache/14ad0946e1c31f94.txt</t>
+          <t>jd_cache/9f6400b899262c75.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1408,16 +1375,12 @@
         </is>
       </c>
       <c r="AA5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB5" t="b">
         <v>0</v>
       </c>
-      <c r="AB5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>geo_restricted</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
           <t>skip</t>
@@ -1425,13 +1388,13 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>"Remote (Americas, UTC-3 to UTC-10)" reads LATAM-open, but the JD states candidates "must be legally authorized to work in the United States" with no sponsorship, which is a US-residency disqualifier regardless of the timezone framing. The role itself is also a hands-on growth-marketing/channel-ops seat (SEO, content, paid channels), a domain and function stretch from Joey's CoS/BizOps/partnerships background.</t>
+          <t>This is a GTM enablement/training manager role reporting to a Director, focused on sales enablement content and curriculum design rather than strategic operator or partnerships work. No LATAM signal and salary band is US-zone-based with no international mention.</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Domain, Function, Geography</t>
+          <t>Function, Domain</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1441,12 +1404,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>geo_restricted</t>
+          <t>Remote-Global-Open</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>$200,000-$250,000</t>
+          <t>$108,650 - $142,224 USD</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1456,25 +1419,21 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Eric (growth strategy owner) - no formal title given</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>zero_to_one</t>
-        </is>
-      </c>
+          <t>Director, GTM Enablement</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AP5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1485,27 +1444,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>nift</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gitlab</t>
+          <t>Nift</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Senior Program Manager, Enterprise Technology &amp; AI</t>
+          <t xml:space="preserve">General Manager, EMEA / UK </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>program</t>
+          <t>market_entry</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Remote, Bangalore</t>
+          <t>Remote, UK</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1550,7 +1509,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1560,12 +1519,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8584282002</t>
+          <t>https://job-boards.greenhouse.io/nift/jobs/4917411007</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-07-06T08:34:18-04:00</t>
+          <t>2026-01-13T16:05:47-05:00</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1591,7 +1550,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>jd_cache/0516b4bb5d9aae63.txt</t>
+          <t>jd_cache/61bf1cb46e9a777e.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1605,16 +1564,12 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AB6" t="b">
         <v>1</v>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>geo_restricted</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
           <t>skip</t>
@@ -1622,13 +1577,17 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>The cross-functional program-management scope (IT/Finance/Legal stakeholders, governance frameworks) echoes Joey's DoD program-management background reasonably well, but the posting is anchored to a specific non-LATAM city, asking "Are you currently based in Bangalore?" This is a hard geographic disqualifier with zero LATAM relevance in the enterprise DevSecOps/IT domain.</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+          <t>Title is General Manager but the body is explicitly a hands-on, quota-carrying sales role building EMEA/UK revenue with no LATAM scope. Requires 12+ years of quota-driven ad-tech sales experience Joey doesn't have, and geography is UK/EMEA, not LATAM.</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>quota_partnerships_disguise</t>
+        </is>
+      </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Domain, Geography</t>
+          <t>Function, Geography</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1638,7 +1597,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>geo_restricted</t>
+          <t>Remote-Global-Open</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1653,25 +1612,21 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>scale_existing</t>
-        </is>
-      </c>
+          <t>global CRO</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -1682,27 +1637,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>aledade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gitlab</t>
+          <t>Aledade</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vice President, Finance Strategy &amp; Operations</t>
+          <t>Director, Payer Go-To-Market (GTM), Remote</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>strategic_ops</t>
+          <t>growth_commercial</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remote, US</t>
+          <t>Remote, United States</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1747,7 +1702,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1757,17 +1712,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8467198002</t>
+          <t>https://jobs.lever.co/aledade/660b03e4-e1db-4ac2-bb9e-c74666f52189</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-06-05T16:18:10-04:00</t>
+          <t>2026-07-07T12:00:31.868000</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Lever</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1788,7 +1743,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>jd_cache/b1fbef6c443cfc44.txt</t>
+          <t>jd_cache/c70c44df4ecea1de.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1819,7 +1774,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Explicitly listed as "Remote, US" with no international-candidate language, so this is a US work-location role outside LATAM scope. It is also a Finance-domain-owned VP role (SOX, revenue recognition, Lead-to-Cash) rather than a general CoS/ops/partnerships mandate.</t>
+          <t>Remote US-based healthcare GTM director role with no LATAM signal; JD explicitly locates the role as Remote, United States with a domain-gated 10-year healthcare requirement. Disqualified on geography.</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -1846,7 +1801,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>CFO</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1855,16 +1810,16 @@
         </is>
       </c>
       <c r="AN7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1875,17 +1830,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hightouch</t>
+          <t>apolloio</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hightouch</t>
+          <t>Apolloio</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Go-to-Market Engineer</t>
+          <t>Go-To-Market Engineer I, SMB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1950,12 +1905,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/hightouch/jobs/5823552004</t>
+          <t>https://job-boards.greenhouse.io/apolloio/jobs/5778017004</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-06-16T17:07:05-04:00</t>
+          <t>2026-07-06T18:51:37-04:00</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1981,7 +1936,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>jd_cache/0e0db98a00b191dc.txt</t>
+          <t>jd_cache/44f748fbd9b679ad.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2012,10 +1967,14 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Location is stated as "Remote, United States" with an E-Verify/I-9 requirement, placing it outside LATAM scope. The role itself is a hands-on technical GTM engineering IC position (Clay, APIs, prompt workflows), not a CoS/Country Manager/senior BD match.</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+          <t>Individual-contributor CSM/RevOps hybrid role explicitly Remote, United States with a 4-year experience bar; not CoS-level and no LATAM scope stated. Disqualified on geography.</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>founding_sales_as_cos</t>
+        </is>
+      </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2029,7 +1988,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>$130,000 - $180,000 USD per year</t>
+          <t>$130,000-$165,000 USD</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2044,11 +2003,11 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>zero_to_one</t>
+          <t>scale_existing</t>
         </is>
       </c>
       <c r="AN8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2057,7 +2016,7 @@
         <v>8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -2068,17 +2027,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>includedhealth</t>
+          <t>apolloio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Includedhealth</t>
+          <t>Apolloio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Go-To-Market Enablement Manager</t>
+          <t>Go-To-Market Engineer II, Mid-Market</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2088,7 +2047,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote, United States</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2143,17 +2102,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/includedhealth/e5475693-8b26-4166-ad01-db9bcbbf2f96</t>
+          <t>https://job-boards.greenhouse.io/apolloio/jobs/5918855004</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-06-26T15:26:50.581000</t>
+          <t>2026-07-06T18:51:37-04:00</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Lever</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2174,7 +2133,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>jd_cache/9f6400b899262c75.txt</t>
+          <t>jd_cache/52d4d3fd7ddd92f2.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2205,7 +2164,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Salary band is scoped to US geographic zones ("Zones A-C"), indicating a US work location despite the bare "Remote" location string. Seniority sits below Director as an individual GTM Enablement Manager, and the function (training/enablement content) is a partial match at best to Joey's CoS/partnerships/ops background.</t>
+          <t>Senior account-management/CS engineer role explicitly Remote, United States with no LATAM scope stated; account-portfolio execution rather than CoS/GM-level mandate. Disqualified on geography.</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -2222,7 +2181,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>$108,650.00 - $142,224.00</t>
+          <t>$150,000-$175,000 USD</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2232,7 +2191,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Director, GTM Enablement</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2250,38 +2209,38 @@
         <v>10</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>portfolio_board:qed-investors</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nift</t>
+          <t>caribou</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nift</t>
+          <t>Caribou</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">General Manager, EMEA / UK </t>
+          <t>Senior Manager, Go-To-Market Operations &amp; Sales Tools</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>market_entry</t>
+          <t>growth_commercial</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Remote, UK</t>
+          <t>Chicago, IL, Denver, CO, Phoenix, AZ, Remote, US</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2336,29 +2295,21 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/nift/jobs/4917411007</t>
+          <t>https://job-boards.greenhouse.io/caribou/jobs/7801514003</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-01-13T16:05:47-05:00</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
+          <t>2026-07-10T15:04:27Z</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>api-live</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
@@ -2367,12 +2318,12 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>jd_cache/61bf1cb46e9a777e.txt</t>
+          <t>jd_cache/4bc951a8358c0c77.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>portfolio_board:qed-investors</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2398,7 +2349,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Role is explicitly scoped to "Remote, UK" / EMEA with country-of-residence and work-authorization screening questions, entirely outside LATAM geography. It also requires a specific must-have background "building out EMEA for an ad-tech company," a domain Joey hasn't worked in.</t>
+          <t>Remote role restricted to a specific list of US states (AZ, CO, DC, IL, MD, TX, VA plus a few conditional others), consumer auto-loan fintech with no LATAM mandate. Disqualified on geography.</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -2415,35 +2366,35 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
+          <t>$120,000-$150,000 USD</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>us_level</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
           <t>not_stated</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>global CRO</t>
-        </is>
-      </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>zero_to_one</t>
+          <t>scale_existing</t>
         </is>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -2454,27 +2405,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pivotal-health</t>
+          <t>firecrawl</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pivotal Health</t>
+          <t>Firecrawl</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Client Strategy &amp; Operations Manager</t>
+          <t>Head of Growth Marketing</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>strategic_ops</t>
+          <t>growth_commercial</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Remote - NY</t>
+          <t>San Francisco, CA (Hybrid) OR Remote (Americas, UTC-3 to UTC-10)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2529,12 +2480,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/pivotal-health/ce4e43d1-7add-408b-ae2d-c1205509527d</t>
+          <t>https://jobs.ashbyhq.com/firecrawl/252206c1-56a2-4598-abef-d2ed9e2295de</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-20T22:25:49.748+00:00</t>
+          <t>2026-07-13T00:04:16.535+00:00</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -2560,7 +2511,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>jd_cache/00f0fa111ce5ea70.txt</t>
+          <t>jd_cache/14ad0946e1c31f94.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -2591,7 +2542,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>JD states candidates "must be authorized to work in the United States without... sponsorship," confirming a US-only work location. The role is also explicitly an individual-contributor position requiring hospital-RCM/IDR domain SME and SQL/BigQuery fluency, a significant domain and technical gap from Joey's background.</t>
+          <t>Growth marketing operator role requires US work authorization explicitly and no sponsorship; while remote Americas UTC-3 to UTC-10 is mentioned, the visa requirement effectively restricts to US-authorized candidates. Also a hands-on channel marketing execution role outside Joey's core function match. Disqualified on geography per US work-authorization requirement.</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -2608,7 +2559,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>$120K - $150K</t>
+          <t>$200,000-$250,000/year (SF-based; adjusted outside US)</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2618,22 +2569,22 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>not_stated</t>
+          <t>Eric (founder, growth strategy owner)</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>scale_existing</t>
+          <t>zero_to_one</t>
         </is>
       </c>
       <c r="AN11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ11" t="n">
         <v>8</v>
@@ -2647,27 +2598,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>remotecom</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remotecom</t>
+          <t>Gitlab</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Global Payroll Implementation Country Lead - Germany</t>
+          <t>Senior Program Manager, Enterprise Technology &amp; AI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>market_entry</t>
+          <t>program</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Remote - DACH</t>
+          <t>Remote, Bangalore</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2692,7 +2643,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2722,12 +2673,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/remotecom/jobs/7735395003</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8584282002</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-05-20T12:43:07-04:00</t>
+          <t>2026-07-06T08:34:18-04:00</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2753,7 +2704,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>jd_cache/64301db3564e8a84.txt</t>
+          <t>jd_cache/0516b4bb5d9aae63.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2784,15 +2735,11 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Role is restricted to 'Remote - DACH,' a specific non-LATAM regional lock with no stated LATAM openness. It is also a payroll-implementation specialist function (DATEV expertise, German legislative knowledge) rather than the CoS/BD/strategic-ops work Joey targets.</t>
+          <t>Role is remote but tied to Bangalore ('Are you currently based in Bangalore?'), an IT/enterprise-systems program management role with no LATAM signal. Skills match is partial (program management, not strategy/BD/CoS) and geography is disqualifying.</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>function, domain</t>
-        </is>
-      </c>
+      <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr">
         <is>
           <t>not_mentioned</t>
@@ -2805,7 +2752,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>approx $77,600-$87,300 (from €71,850-€80,800 EUR)</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2815,7 +2762,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Manager, Payroll Operations</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -2824,16 +2771,16 @@
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>8</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -2844,17 +2791,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rula</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rula</t>
+          <t>Gitlab</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Strategy &amp; Operations Manager  (Remote)</t>
+          <t>Vice President, Finance Strategy &amp; Operations</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2864,7 +2811,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote, US</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2909,7 +2856,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2919,17 +2866,17 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/rula/3013fcdb-0e71-42f2-b3f1-7e8e3b3a2c44</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8467198002</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-06-18T19:42:02.894+00:00</t>
+          <t>2026-06-05T16:18:10-04:00</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Ashby</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2950,7 +2897,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>jd_cache/8b31a0d5dbd4b5fb.txt</t>
+          <t>jd_cache/b1fbef6c443cfc44.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2981,15 +2928,11 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>JD explicitly states the company hires only within the U.S. ('must be based in United States, currently not hiring in Hawaii'), which is a hard geo_restricted disqualifier regardless of fit. Underlying function (strategy &amp; ops, data-driven programs) is a partial skills match but the mental-healthcare sector isn't among Joey's priority verticals.</t>
+          <t>Explicitly 'Remote, US' with no international candidate language, disqualifying despite strong VP-level finance strategy fit. Role is finance-transformation focused, a domain stretch from Joey's background.</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>geography</t>
-        </is>
-      </c>
+      <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr">
         <is>
           <t>not_mentioned</t>
@@ -3002,35 +2945,31 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>$136,170-$152,190</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>us_level</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>scale_existing</t>
-        </is>
-      </c>
+          <t>CFO</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -3041,27 +2980,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>upwork</t>
+          <t>remotecom</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Upwork</t>
+          <t>Remotecom</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sr Director, Corporate Development</t>
+          <t>Global Payroll Implementation Country Lead - Germany</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>growth_commercial</t>
+          <t>market_entry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palo Alto, California, United States; Remote</t>
+          <t>Remote - DACH</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3086,7 +3025,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -3106,7 +3045,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3116,12 +3055,12 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/upwork/jobs/7110133003</t>
+          <t>https://job-boards.greenhouse.io/remotecom/jobs/7735395003</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-05-11T14:20:37-04:00</t>
+          <t>2026-05-20T12:43:07-04:00</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -3147,7 +3086,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>jd_cache/4421f1e7876e2e3f.txt</t>
+          <t>jd_cache/64301db3564e8a84.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -3178,15 +3117,11 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>JD asks for current/planned U.S. state of residence and the company hires full-time only across 34 U.S. states, a geo_restricted disqualifier with no LATAM or international remote path stated. Sr. Director-level scope and executive exposure fit Joey's seniority, but hands-on M&amp;A/corp-dev deal execution is a domain stretch beyond his banking and partnerships background.</t>
+          <t>This is a Germany-specific payroll implementation specialist role requiring deep German payroll/DATEV expertise, not a strategic operator function. Region is DACH, not LATAM, so it is geo-restricted.</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>domain, geography</t>
-        </is>
-      </c>
+      <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr">
         <is>
           <t>not_mentioned</t>
@@ -3199,17 +3134,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>$195,000-$362,000</t>
+          <t>€71,850 - €80,800 EUR</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>us_level</t>
+          <t>latam_local</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>VP of Strategy, Corporate Development &amp; Partnerships</t>
+          <t>Manager, Payroll Operations</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -3218,15 +3153,771 @@
         </is>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AQ14" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>rula</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Rula</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Strategy &amp; Operations Manager  (Remote)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>strategic_ops</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>L?, D?, P?</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>needs_verification</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/rula/3013fcdb-0e71-42f2-b3f1-7e8e3b3a2c44</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-06-18T19:42:02.894+00:00</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>api-live</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>jd_cache/8b31a0d5dbd4b5fb.txt</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>REPEAT</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>geo_restricted</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Strategy &amp; Ops Manager role is remote but explicitly US-only hiring with no LATAM scope, so it is geo-restricted despite reasonable functional fit. Sector is health-tech quality operations, not a strong fintech/defense fit.</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>not_mentioned</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>geo_restricted</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>$136,170 - $152,190 USD</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>us_level</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>scale_existing</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>upwork</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Upwork</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sr Director, Corporate Development</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>growth_commercial</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Palo Alto, California, United States; Remote</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>L?, D?, P?</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>needs_verification</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/upwork/jobs/7110133003</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026-05-11T14:20:37-04:00</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>api-live</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>jd_cache/4421f1e7876e2e3f.txt</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>REPEAT</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>geo_restricted</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Senior Director Corporate Development is a strong seniority and functional match, but hiring is limited to 34 US states with no LATAM residency option, making it geo-restricted.</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>not_mentioned</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>geo_restricted</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>$195,000 - $362,000 USD</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>us_level</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>VP of Strategy, Corporate Development &amp; Partnerships</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>scale_existing</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>portfolio_board:a16z</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>talkiatry</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>talkiatry</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>General Manager/Director of Clinical Operations, Psychiatry</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>market_entry</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>United States, Remote</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>L?, D?, P?</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/talkiatry/f13dbc0c-63b4-4e75-bf24-91f0c87ce3e5?utm_source=jobs.a16z.com</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2026-07-15T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>jd_cache/db072d64e2033f6d.txt</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>portfolio_board:a16z</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>REPEAT</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>geo_restricted</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Remote (US) with no LATAM scope or international candidate language, and E-Verify/I-9 requirement signals US work authorization only; also healthcare operations sector is a weak fit for Joey's background. Disqualified on geography despite reasonable operations/GM skills match.</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>not_mentioned</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>geo_restricted</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>$165K - $175K</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>us_level</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>scale_existing</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>portfolio_board:kaszek</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>wellhub</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>wellhub</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Partnerships Director – US National Partnerships</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>partnerships_bd</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>US (Remote)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>L?, D?, P?</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gympass/jobs/8444113002</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2026-03-05T23:49:33Z</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>jd_cache/246f403e48ce2b1d.txt</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>portfolio_board:kaszek</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>REPEAT</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>geo_restricted</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Role is explicitly restricted to a specific list of US states with no LATAM or international mention, disqualifying on geography despite a strong partnerships/BD skills match. Title says Partnerships Director but body emphasizes managing enterprise account volume and negotiation rather than zero-to-one building.</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>quota_partnerships_disguise</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>not_mentioned</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>geo_restricted</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>$160,000 - $175,000</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>us_level</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Senior Director of Partnerships</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>scale_existing</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>9</v>
       </c>
     </row>

--- a/results/joey/LATAM/Week_of_2026-07-20/Scored_LATAM_Joey_Complete_2026-07-20.xlsx
+++ b/results/joey/LATAM/Week_of_2026-07-20/Scored_LATAM_Joey_Complete_2026-07-20.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -41,12 +41,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2A44"/>
         <bgColor rgb="001F2A44"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
-        <bgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,10 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ18"/>
+  <dimension ref="A1:AR18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -460,23 +453,24 @@
     <col width="31" customWidth="1" min="24" max="24"/>
     <col width="31" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
     <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="29" customWidth="1" min="32" max="32"/>
-    <col width="21" customWidth="1" min="33" max="33"/>
-    <col width="21" customWidth="1" min="34" max="34"/>
-    <col width="20" customWidth="1" min="35" max="35"/>
-    <col width="45" customWidth="1" min="36" max="36"/>
-    <col width="16" customWidth="1" min="37" max="37"/>
-    <col width="45" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
-    <col width="17" customWidth="1" min="40" max="40"/>
-    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="45" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="45" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
+    <col width="45" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="45" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
-    <col width="17" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="43" max="43"/>
+    <col width="17" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -612,85 +606,90 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_week</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>capped</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>disqualified</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>recommend</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>rationale</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>red_flags</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>stretch_dimensions</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>spanish_requirement</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>location_type</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>salary_usd</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>comp_band_type</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>reports_to</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>builder_vs_manager</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>subscore_skills</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>subscore_geography</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>subscore_seniority</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>subscore_sector</t>
         </is>
@@ -811,97 +810,106 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA2" t="n">
-        <v>83</v>
-      </c>
-      <c r="AB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Director of Business Development for a stablecoin/cross-border fintech based in Mexico City is a direct sector, seniority, and geography match to Joey's background in startup banking and partnerships. Spanish fluency is explicitly required, which flags but doesn't disqualify given his active learning.</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Title says Director of BD but body is a quota-carrying sales role requiring existing deep network in crypto/fintech cross-border payments, reporting to Head of Sales rather than executive scope. Strong fintech/LATAM geographic fit is undercut by IC-heavy sales function and required Spanish fluency.</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>quota_partnerships_disguise</t>
+        </is>
+      </c>
       <c r="AH2" t="inlineStr">
         <is>
+          <t>Function, Compensation-adjacent quota structure</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>required</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>CDMX-Based</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>not_stated (OTE-based, commission + base)</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
           <t>Head of Sales</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>zero_to_one</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>30</v>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>scale_existing</t>
+        </is>
       </c>
       <c r="AO2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AP2" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>portfolio_board:a16z</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>firecrawl</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Firecrawl</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Strategic Programs Lead, New Markets</t>
+          <t>Head of Growth Marketing</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>strategic_ops</t>
+          <t>growth_commercial</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>US-Remote</t>
+          <t>San Francisco, CA (Hybrid) OR Remote (Americas, UTC-3 to UTC-10)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -946,7 +954,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -956,21 +964,29 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8070648</t>
+          <t>https://jobs.ashbyhq.com/firecrawl/252206c1-56a2-4598-abef-d2ed9e2295de</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-07-16T21:33:48Z</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
+          <t>2026-07-13T00:04:16.535+00:00</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>api-live</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
@@ -979,12 +995,12 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>jd_cache/27c007c7f953372d.txt</t>
+          <t>jd_cache/14ad0946e1c31f94.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>portfolio_board:a16z</t>
+          <t>api</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -992,70 +1008,71 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA3" t="n">
-        <v>58</v>
-      </c>
-      <c r="AB3" t="b">
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC3" t="b">
         <v>1</v>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Strong functional match as a 0-to-1 strategic program lead at a fintech (Stripe) with explicit new-markets/Americas &amp; EMEA scope, but the role is US-remote with no LATAM residency path and requires deep risk/compliance program management domain not on Joey's resume. Two stretches (geography, domain) cap the score.</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Geography, Domain</t>
-        </is>
-      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Remote Americas timezone scope gives real geographic fit, but this is a hands-on growth-marketing channel-execution role, not a strategy/CoS/partnerships mandate, and requires deep developer-tool marketing execution Joey hasn't demonstrated. Two stretch dimensions (Function, Domain) cap the score.</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>Function, Domain</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Remote-Global-Open</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>$127,600 - $191,400 USD</t>
+          <t>Remote-Americas</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
+          <t>$200,000-$250,000/year (US-based; adjusted for cost of living elsewhere)</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
           <t>us_level</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>not_stated</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>zero_to_one</t>
         </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>28</v>
       </c>
       <c r="AO3" t="n">
         <v>14</v>
       </c>
       <c r="AP3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -1066,27 +1083,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pivotal-health</t>
+          <t>nift</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pivotal Health</t>
+          <t>Nift</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Client Strategy &amp; Operations Manager</t>
+          <t xml:space="preserve">General Manager, EMEA / UK </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>strategic_ops</t>
+          <t>market_entry</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Remote - NY</t>
+          <t>Remote, UK</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1131,7 +1148,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1141,17 +1158,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/pivotal-health/ce4e43d1-7add-408b-ae2d-c1205509527d</t>
+          <t>https://job-boards.greenhouse.io/nift/jobs/4917411007</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-20T22:25:49.748+00:00</t>
+          <t>2026-01-13T16:05:47-05:00</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Ashby</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1172,7 +1189,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>jd_cache/00f0fa111ce5ea70.txt</t>
+          <t>jd_cache/61bf1cb46e9a777e.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1185,65 +1202,74 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Individual-contributor client strategy/ops role requiring deep hospital revenue-cycle SME experience and strong SQL/BigQuery fluency Joey doesn't demonstrate, with US-only work authorization required and no LATAM signal.</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Title is General Manager but body is almost entirely quota-carrying ad-tech performance-marketing sales in EMEA/UK, a domain-gated sector with no LATAM scope, matching the quota_partnerships_disguise archetype. Remote UK-based with no LATAM signal caps geography low, and the ad-tech quota-sales function/domain combination represents two stretches, capping the score.</t>
+        </is>
+      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>quota_partnerships_disguise</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
           <t>Function, Domain</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>Remote-Global-Open</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>$120,000 - $150,000 USD</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>us_level</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="n">
-        <v>22</v>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>global CRO</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>zero_to_one</t>
+        </is>
       </c>
       <c r="AO4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR4" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1255,27 +1281,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>includedhealth</t>
+          <t>pivotal-health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Includedhealth</t>
+          <t>Pivotal Health</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Go-To-Market Enablement Manager</t>
+          <t>Client Strategy &amp; Operations Manager</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>growth_commercial</t>
+          <t>strategic_ops</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote - NY</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1320,7 +1346,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1330,17 +1356,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/includedhealth/e5475693-8b26-4166-ad01-db9bcbbf2f96</t>
+          <t>https://jobs.ashbyhq.com/pivotal-health/ce4e43d1-7add-408b-ae2d-c1205509527d</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-06-26T15:26:50.581000</t>
+          <t>2026-05-20T22:25:49.748+00:00</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Lever</t>
+          <t>Ashby</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1361,7 +1387,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>jd_cache/9f6400b899262c75.txt</t>
+          <t>jd_cache/00f0fa111ce5ea70.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1374,66 +1400,71 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB5" t="b">
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC5" t="b">
         <v>0</v>
       </c>
-      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
+          <t>geo_restricted</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>This is a GTM enablement/training manager role reporting to a Director, focused on sales enablement content and curriculum design rather than strategic operator or partnerships work. No LATAM signal and salary band is US-zone-based with no international mention.</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Function, Domain</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Requires US work authorization with no sponsorship and is healthtech-RCM specific, a domain outside Joey's background; no LATAM signal makes this geo_restricted.</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Remote-Global-Open</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>$108,650 - $142,224 USD</t>
+          <t>geo_restricted</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
+          <t>$120K-$150K</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
           <t>us_level</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Director, GTM Enablement</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="n">
-        <v>18</v>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>scale_existing</t>
+        </is>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1444,27 +1475,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nift</t>
+          <t>rula</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nift</t>
+          <t>Rula</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">General Manager, EMEA / UK </t>
+          <t>Strategy &amp; Operations Manager  (Remote)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>market_entry</t>
+          <t>strategic_ops</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Remote, UK</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1519,17 +1550,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/nift/jobs/4917411007</t>
+          <t>https://jobs.ashbyhq.com/rula/3013fcdb-0e71-42f2-b3f1-7e8e3b3a2c44</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-01-13T16:05:47-05:00</t>
+          <t>2026-06-18T19:42:02.894+00:00</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Ashby</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1550,7 +1581,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>jd_cache/61bf1cb46e9a777e.txt</t>
+          <t>jd_cache/8b31a0d5dbd4b5fb.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1563,70 +1594,71 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA6" t="n">
-        <v>35</v>
-      </c>
-      <c r="AB6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC6" t="b">
+        <v>0</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
+          <t>geo_restricted</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Title is General Manager but the body is explicitly a hands-on, quota-carrying sales role building EMEA/UK revenue with no LATAM scope. Requires 12+ years of quota-driven ad-tech sales experience Joey doesn't have, and geography is UK/EMEA, not LATAM.</t>
-        </is>
-      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>quota_partnerships_disguise</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Function, Geography</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
+          <t>Role explicitly requires US-based residency (excluding Hawaii) with no LATAM or international option stated, and is a healthtech quality-analytics IC role outside Joey's core partnerships/CoS positioning.</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Remote-Global-Open</t>
-        </is>
-      </c>
       <c r="AJ6" t="inlineStr">
         <is>
+          <t>geo_restricted</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>$136,170-$152,190</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>us_level</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
           <t>not_stated</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>global CRO</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="n">
-        <v>22</v>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>scale_existing</t>
+        </is>
       </c>
       <c r="AO6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AP6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -1756,70 +1788,71 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA7" t="n">
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="n">
         <v>0</v>
       </c>
-      <c r="AB7" t="b">
+      <c r="AC7" t="b">
         <v>0</v>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>Remote US-based healthcare GTM director role with no LATAM signal; JD explicitly locates the role as Remote, United States with a domain-gated 10-year healthcare requirement. Disqualified on geography.</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Remote US healthcare payer GTM role with no LATAM signal whatsoever; disqualified on geography despite reasonable seniority/skills alignment. Also highly domain-gated to healthcare value-based care, a real domain stretch for Joey.</t>
+        </is>
+      </c>
       <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>not_stated</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
           <t>not_stated</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>scale_existing</t>
         </is>
       </c>
-      <c r="AN7" t="n">
+      <c r="AO7" t="n">
         <v>20</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AP7" t="n">
         <v>0</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AQ7" t="n">
         <v>18</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>10</v>
+      <c r="AR7" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1949,73 +1982,74 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA8" t="n">
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="n">
         <v>0</v>
       </c>
-      <c r="AB8" t="b">
+      <c r="AC8" t="b">
         <v>0</v>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>Individual-contributor CSM/RevOps hybrid role explicitly Remote, United States with a 4-year experience bar; not CoS-level and no LATAM scope stated. Disqualified on geography.</t>
-        </is>
-      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>founding_sales_as_cos</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr">
+          <t>Remote US-only IC customer success/GTM engineering role focused on account book management with no LATAM scope, disqualifying it on geography. Title implies strategic GTM but body is quota-adjacent account management well below Joey's seniority level.</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>quota_partnerships_disguise</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>$130,000-$165,000 USD</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
+          <t>$130,000-$165,000 USD (OTE)</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
           <t>us_level</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>not_stated</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>scale_existing</t>
         </is>
       </c>
-      <c r="AN8" t="n">
-        <v>12</v>
-      </c>
       <c r="AO8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP8" t="n">
         <v>0</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AQ8" t="n">
         <v>8</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AR8" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2146,69 +2180,70 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="n">
         <v>0</v>
       </c>
-      <c r="AB9" t="b">
+      <c r="AC9" t="b">
         <v>0</v>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>Senior account-management/CS engineer role explicitly Remote, United States with no LATAM scope stated; account-portfolio execution rather than CoS/GM-level mandate. Disqualified on geography.</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Remote US enterprise CSM/account management role with no LATAM scope stated, disqualifying on geography. Individual-contributor account ownership structure is below Joey's demonstrated director/VP-level scope.</t>
+        </is>
+      </c>
       <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr">
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>$150,000-$175,000 USD</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
+          <t>$150,000-$175,000 USD (OTE)</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
           <t>us_level</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>not_stated</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>scale_existing</t>
         </is>
       </c>
-      <c r="AN9" t="n">
-        <v>14</v>
-      </c>
       <c r="AO9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP9" t="n">
         <v>0</v>
       </c>
-      <c r="AP9" t="n">
-        <v>10</v>
-      </c>
       <c r="AQ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2331,69 +2366,70 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="n">
         <v>0</v>
       </c>
-      <c r="AB10" t="b">
+      <c r="AC10" t="b">
         <v>0</v>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>Remote role restricted to a specific list of US states (AZ, CO, DC, IL, MD, TX, VA plus a few conditional others), consumer auto-loan fintech with no LATAM mandate. Disqualified on geography.</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Remote restricted to a specific list of US states with no LATAM scope, disqualifying on geography despite a reasonably strong operations/strategy skills match. Sales tools/dialer operations focus is also a consumer auto-lending sector poor fit.</t>
+        </is>
+      </c>
       <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr">
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>$120,000-$150,000 USD</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>us_level</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>not_stated</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>scale_existing</t>
         </is>
       </c>
-      <c r="AN10" t="n">
-        <v>22</v>
-      </c>
       <c r="AO10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP10" t="n">
         <v>0</v>
       </c>
-      <c r="AP10" t="n">
-        <v>14</v>
-      </c>
       <c r="AQ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2405,27 +2441,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>firecrawl</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Firecrawl</t>
+          <t>Gitlab</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Head of Growth Marketing</t>
+          <t>Senior Program Manager, Enterprise Technology &amp; AI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>growth_commercial</t>
+          <t>program</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Francisco, CA (Hybrid) OR Remote (Americas, UTC-3 to UTC-10)</t>
+          <t>Remote, Bangalore</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2470,7 +2506,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2480,17 +2516,17 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/firecrawl/252206c1-56a2-4598-abef-d2ed9e2295de</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8584282002</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-07-13T00:04:16.535+00:00</t>
+          <t>2026-07-06T08:34:18-04:00</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Ashby</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -2511,7 +2547,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>jd_cache/14ad0946e1c31f94.txt</t>
+          <t>jd_cache/0516b4bb5d9aae63.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -2524,69 +2560,70 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA11" t="n">
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="n">
         <v>0</v>
       </c>
-      <c r="AB11" t="b">
+      <c r="AC11" t="b">
         <v>0</v>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>Growth marketing operator role requires US work authorization explicitly and no sponsorship; while remote Americas UTC-3 to UTC-10 is mentioned, the visa requirement effectively restricts to US-authorized candidates. Also a hands-on channel marketing execution role outside Joey's core function match. Disqualified on geography per US work-authorization requirement.</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Role is remote but tied to Bangalore-based hiring (candidates asked if based in Bangalore), with no LATAM signal. Enterprise IT program management is a partial functional match but the role is disqualified on geography.</t>
+        </is>
+      </c>
       <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr">
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>$200,000-$250,000/year (SF-based; adjusted outside US)</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>us_level</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Eric (founder, growth strategy owner)</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>zero_to_one</t>
-        </is>
-      </c>
-      <c r="AN11" t="n">
-        <v>18</v>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>scale_existing</t>
+        </is>
       </c>
       <c r="AO11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP11" t="n">
         <v>0</v>
       </c>
-      <c r="AP11" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR11" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2608,17 +2645,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Senior Program Manager, Enterprise Technology &amp; AI</t>
+          <t>Vice President, Finance Strategy &amp; Operations</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>program</t>
+          <t>strategic_ops</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Remote, Bangalore</t>
+          <t>Remote, US</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2673,12 +2710,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8584282002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8467198002</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-07-06T08:34:18-04:00</t>
+          <t>2026-06-05T16:18:10-04:00</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2704,7 +2741,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>jd_cache/0516b4bb5d9aae63.txt</t>
+          <t>jd_cache/b1fbef6c443cfc44.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2717,70 +2754,71 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA12" t="n">
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="n">
         <v>0</v>
       </c>
-      <c r="AB12" t="b">
+      <c r="AC12" t="b">
         <v>0</v>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>Role is remote but tied to Bangalore ('Are you currently based in Bangalore?'), an IT/enterprise-systems program management role with no LATAM signal. Skills match is partial (program management, not strategy/BD/CoS) and geography is disqualifying.</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Explicitly 'Remote, US' with no LATAM scope or international candidate language, so it is geo-restricted despite strong VP-level seniority match. Deep finance-transformation domain expertise (Lead-to-Cash, SOX, consumption billing) is also a significant domain stretch beyond Joey's banking/VC background.</t>
+        </is>
+      </c>
       <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr">
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AK12" t="inlineStr">
         <is>
           <t>not_stated</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>not_stated</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
+          <t>CFO</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
           <t>scale_existing</t>
         </is>
       </c>
-      <c r="AN12" t="n">
+      <c r="AO12" t="n">
         <v>20</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AP12" t="n">
         <v>0</v>
       </c>
-      <c r="AP12" t="n">
-        <v>13</v>
-      </c>
       <c r="AQ12" t="n">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -2791,27 +2829,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>hightouch</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gitlab</t>
+          <t>Hightouch</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Vice President, Finance Strategy &amp; Operations</t>
+          <t>Go-to-Market Engineer</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>strategic_ops</t>
+          <t>growth_commercial</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Remote, US</t>
+          <t>Remote, United States</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2856,7 +2894,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2866,12 +2904,12 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8467198002</t>
+          <t>https://job-boards.greenhouse.io/hightouch/jobs/5823552004</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-06-05T16:18:10-04:00</t>
+          <t>2026-06-16T17:07:05-04:00</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2897,7 +2935,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>jd_cache/b1fbef6c443cfc44.txt</t>
+          <t>jd_cache/0e0db98a00b191dc.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2910,65 +2948,70 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="n">
         <v>0</v>
       </c>
-      <c r="AB13" t="b">
+      <c r="AC13" t="b">
         <v>0</v>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>Explicitly 'Remote, US' with no international candidate language, disqualifying despite strong VP-level finance strategy fit. Role is finance-transformation focused, a domain stretch from Joey's background.</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Posted as 'Remote, United States' with US work-authorization requirements, disqualifying on geography. Also an individual-contributor technical builder role (Clay, Claude, RevOps tooling) well below Joey's stated seniority level.</t>
+        </is>
+      </c>
       <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr">
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AJ13" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>$130,000-$180,000 USD (OTE)</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>us_level</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
         <is>
           <t>not_stated</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>CFO</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="n">
-        <v>24</v>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>zero_to_one</t>
+        </is>
       </c>
       <c r="AO13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP13" t="n">
         <v>0</v>
       </c>
-      <c r="AP13" t="n">
-        <v>18</v>
-      </c>
       <c r="AQ13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2980,27 +3023,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>remotecom</t>
+          <t>includedhealth</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remotecom</t>
+          <t>Includedhealth</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Global Payroll Implementation Country Lead - Germany</t>
+          <t>Go-To-Market Enablement Manager</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>market_entry</t>
+          <t>growth_commercial</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Remote - DACH</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3025,7 +3068,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -3045,7 +3088,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3055,17 +3098,17 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/remotecom/jobs/7735395003</t>
+          <t>https://jobs.lever.co/includedhealth/e5475693-8b26-4166-ad01-db9bcbbf2f96</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-05-20T12:43:07-04:00</t>
+          <t>2026-06-26T15:26:50.581000</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Lever</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -3086,7 +3129,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>jd_cache/64301db3564e8a84.txt</t>
+          <t>jd_cache/9f6400b899262c75.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -3099,70 +3142,71 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="n">
         <v>0</v>
       </c>
-      <c r="AB14" t="b">
+      <c r="AC14" t="b">
         <v>0</v>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>This is a Germany-specific payroll implementation specialist role requiring deep German payroll/DATEV expertise, not a strategic operator function. Region is DACH, not LATAM, so it is geo-restricted.</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Salary bands are explicitly tied to US cost-of-labor zones (Phoenix, Chicago, etc.) with no LATAM or international remote option, disqualifying on geography. Manager-level reporting to a Director and healthcare-specific domain requirement also limit fit.</t>
+        </is>
+      </c>
       <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr">
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>€71,850 - €80,800 EUR</t>
-        </is>
-      </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>latam_local</t>
+          <t>$108,650-$142,224 USD (Zones A-C)</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Manager, Payroll Operations</t>
+          <t>us_level</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
+          <t>Director, GTM Enablement</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
           <t>scale_existing</t>
         </is>
       </c>
-      <c r="AN14" t="n">
-        <v>10</v>
-      </c>
       <c r="AO14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP14" t="n">
         <v>0</v>
       </c>
-      <c r="AP14" t="n">
-        <v>13</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -3173,52 +3217,52 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rula</t>
+          <t>remotecom</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rula</t>
+          <t>Remotecom</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Strategy &amp; Operations Manager  (Remote)</t>
+          <t>Global Payroll Implementation Country Lead - Germany</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>strategic_ops</t>
+          <t>market_entry</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - EMEA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>L?, D?, P?</t>
+          <t>P</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>false</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -3238,7 +3282,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3248,17 +3292,17 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/rula/3013fcdb-0e71-42f2-b3f1-7e8e3b3a2c44</t>
+          <t>https://job-boards.greenhouse.io/remotecom/jobs/7741670003</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-06-18T19:42:02.894+00:00</t>
+          <t>2026-05-20T12:43:21-04:00</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Ashby</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -3279,7 +3323,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>jd_cache/8b31a0d5dbd4b5fb.txt</t>
+          <t>jd_cache/6942018b9b8aad47.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3289,104 +3333,109 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>REPEAT</t>
-        </is>
-      </c>
-      <c r="AA15" t="n">
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
         <v>0</v>
       </c>
-      <c r="AB15" t="b">
+      <c r="AC15" t="b">
         <v>0</v>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>Strategy &amp; Ops Manager role is remote but explicitly US-only hiring with no LATAM scope, so it is geo-restricted despite reasonable functional fit. Sector is health-tech quality operations, not a strong fintech/defense fit.</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>This is a Germany-specific payroll implementation lead role requiring deep German payroll/DATEV expertise, entirely outside Joey's skill set and with no LATAM geographic tie despite EOR sector adjacency.</t>
+        </is>
+      </c>
       <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr">
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AJ15" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>$136,170 - $152,190 USD</t>
-        </is>
-      </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>us_level</t>
+          <t>€71,850-€80,800 EUR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>not_stated</t>
+          <t>latam_local</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
+          <t>Manager, Payroll Operations</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
           <t>scale_existing</t>
         </is>
       </c>
-      <c r="AN15" t="n">
-        <v>22</v>
-      </c>
       <c r="AO15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP15" t="n">
         <v>0</v>
       </c>
-      <c r="AP15" t="n">
-        <v>13</v>
-      </c>
       <c r="AQ15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR15" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>portfolio_board:a16z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>upwork</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Upwork</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sr Director, Corporate Development</t>
+          <t>Strategy and Operations Lead, Deal Pricing</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>growth_commercial</t>
+          <t>strategic_ops</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Palo Alto, California, United States; Remote</t>
+          <t>US-Remote</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3441,29 +3490,21 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/upwork/jobs/7110133003</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8044391</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-05-11T14:20:37-04:00</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
+          <t>2026-07-20T22:43:18Z</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>api-live</t>
-        </is>
-      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
@@ -3472,114 +3513,119 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>jd_cache/4421f1e7876e2e3f.txt</t>
+          <t>jd_cache/25de98b90637aedf.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>portfolio_board:a16z</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>REPEAT</t>
-        </is>
-      </c>
-      <c r="AA16" t="n">
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
         <v>0</v>
       </c>
-      <c r="AB16" t="b">
+      <c r="AC16" t="b">
         <v>0</v>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>Senior Director Corporate Development is a strong seniority and functional match, but hiring is limited to 34 US states with no LATAM residency option, making it geo-restricted.</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Strong Chief-of-Staff-style fintech role with excellent skills fit, but the JD frames remote as 35+ miles from a US Stripe office with no international/any-location language, making it US-geo-restricted despite the fintech sector match.</t>
+        </is>
+      </c>
       <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr">
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>$195,000 - $362,000 USD</t>
-        </is>
-      </c>
       <c r="AK16" t="inlineStr">
         <is>
+          <t>$132,000-$198,000</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
           <t>us_level</t>
         </is>
       </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>VP of Strategy, Corporate Development &amp; Partnerships</t>
-        </is>
-      </c>
       <c r="AM16" t="inlineStr">
         <is>
+          <t>Deal Pricing leadership (Chief of Staff-style function)</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
           <t>scale_existing</t>
         </is>
       </c>
-      <c r="AN16" t="n">
-        <v>26</v>
-      </c>
       <c r="AO16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP16" t="n">
         <v>0</v>
       </c>
-      <c r="AP16" t="n">
-        <v>18</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>portfolio_board:a16z</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>talkiatry</t>
+          <t>upwork</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>talkiatry</t>
+          <t>Upwork</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>General Manager/Director of Clinical Operations, Psychiatry</t>
+          <t>Sr Director, Corporate Development</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>market_entry</t>
+          <t>growth_commercial</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>United States, Remote</t>
+          <t>Palo Alto, California, United States; Remote</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3607,7 +3653,11 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -3625,31 +3675,35 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>needs_verification</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/talkiatry/f13dbc0c-63b4-4e75-bf24-91f0c87ce3e5?utm_source=jobs.a16z.com</t>
+          <t>https://job-boards.greenhouse.io/upwork/jobs/7110133003</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-07-15T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
+          <t>2026-05-11T14:20:37-04:00</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>api-live</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>success</t>
@@ -3657,12 +3711,12 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>jd_cache/db072d64e2033f6d.txt</t>
+          <t>jd_cache/4421f1e7876e2e3f.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>portfolio_board:a16z</t>
+          <t>api</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -3670,101 +3724,102 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" t="b">
+      <c r="AC17" t="b">
         <v>0</v>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>Remote (US) with no LATAM scope or international candidate language, and E-Verify/I-9 requirement signals US work authorization only; also healthcare operations sector is a weak fit for Joey's background. Disqualified on geography despite reasonable operations/GM skills match.</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Senior corporate development/M&amp;A role hires only in 34 US states with no LATAM or international remote option, and the deep M&amp;A/PE deal-execution focus is a domain stretch beyond Joey's partnerships-and-BD background.</t>
+        </is>
+      </c>
       <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr">
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>$165K - $175K</t>
-        </is>
-      </c>
       <c r="AK17" t="inlineStr">
         <is>
+          <t>$195,000-$362,000</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
           <t>us_level</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
       <c r="AM17" t="inlineStr">
         <is>
+          <t>VP of Strategy, Corporate Development &amp; Partnerships</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
           <t>scale_existing</t>
         </is>
       </c>
-      <c r="AN17" t="n">
-        <v>24</v>
-      </c>
       <c r="AO17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP17" t="n">
         <v>0</v>
       </c>
-      <c r="AP17" t="n">
-        <v>15</v>
-      </c>
       <c r="AQ17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR17" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>portfolio_board:kaszek</t>
+          <t>portfolio_board:a16z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>wellhub</t>
+          <t>talkiatry</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>wellhub</t>
+          <t>talkiatry</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Partnerships Director – US National Partnerships</t>
+          <t>General Manager/Director of Clinical Operations, Psychiatry</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>partnerships_bd</t>
+          <t>market_entry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>US (Remote)</t>
+          <t>United States, Remote</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3815,12 +3870,12 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gympass/jobs/8444113002</t>
+          <t>https://jobs.ashbyhq.com/talkiatry/f13dbc0c-63b4-4e75-bf24-91f0c87ce3e5?utm_source=jobs.a16z.com</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-03-05T23:49:33Z</t>
+          <t>2026-07-15T00:00:00Z</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
@@ -3830,7 +3885,11 @@
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>success</t>
@@ -3838,12 +3897,12 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>jd_cache/246f403e48ce2b1d.txt</t>
+          <t>jd_cache/db072d64e2033f6d.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>portfolio_board:kaszek</t>
+          <t>portfolio_board:a16z</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -3851,73 +3910,70 @@
           <t>REPEAT</t>
         </is>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="n">
         <v>0</v>
       </c>
-      <c r="AB18" t="b">
+      <c r="AC18" t="b">
         <v>0</v>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>Role is explicitly restricted to a specific list of US states with no LATAM or international mention, disqualifying on geography despite a strong partnerships/BD skills match. Title says Partnerships Director but body emphasizes managing enterprise account volume and negotiation rather than zero-to-one building.</t>
-        </is>
-      </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>quota_partnerships_disguise</t>
+          <t>Role requires US work authorization via E-Verify and Form I-9, with no LATAM or international candidate language, making it geo-restricted despite strong operational and P&amp;L ownership fit. Domain (healthcare/psychiatry) also has no stated LATAM relevance.</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr">
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
         <is>
           <t>not_mentioned</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>geo_restricted</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>$160,000 - $175,000</t>
-        </is>
-      </c>
       <c r="AK18" t="inlineStr">
         <is>
+          <t>$165K-$175K + bonus</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
           <t>us_level</t>
         </is>
       </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Senior Director of Partnerships</t>
-        </is>
-      </c>
       <c r="AM18" t="inlineStr">
         <is>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
           <t>scale_existing</t>
         </is>
       </c>
-      <c r="AN18" t="n">
+      <c r="AO18" t="n">
         <v>26</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AP18" t="n">
         <v>0</v>
       </c>
-      <c r="AP18" t="n">
-        <v>17</v>
-      </c>
       <c r="AQ18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR18" t="n">
         <v>9</v>
       </c>
     </row>
